--- a/data/import/3m.xlsx
+++ b/data/import/3m.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U189"/>
+  <dimension ref="A1:V189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +522,11 @@
           <t>pub</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>tds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -605,6 +610,11 @@
       <c r="U2" t="n">
         <v>0</v>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396565O/3m-tamper-indicating-label-material-7937.pdf?&amp;fn=3M-Tamper-Indicating-Label-Material-7937.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -694,6 +704,11 @@
       <c r="U3" t="n">
         <v>1</v>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1571172O/3m-aluminum-foil-label-material-7800.pdf?&amp;fn=3M-Aluminum-Foil-Label-Material-7800.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -777,6 +792,11 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399725O/3m-dot-matrix-printable-polyimide-label-material-7811.pdf?&amp;fn=3M-Dot-Matrix-Printable-Polyimide-Label-Material-7811.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -860,6 +880,11 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399667O/3m-thermal-transfer-polyimide-label-material-7812.pdf?&amp;fn=3M-Thermal-Transfer-Polyimide-Label-Material-7812.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -944,6 +969,11 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396595O/3m-void-polyester-durable-label-material-fmv02.pdf?&amp;fn=3M-Void-Polyester-Durable-Label-Material-FMV02.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1028,6 +1058,11 @@
       <c r="U7" t="n">
         <v>1</v>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396556O/3m-polyester-overlaminating-film-7731fl.pdf?&amp;fn=3M-Polyester-Overlaminating-Film-7731FL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1206,6 +1241,11 @@
       <c r="U9" t="n">
         <v>1</v>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399683O/3m-thermal-transfer-polyester-label-material-7815fl.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7815FL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1290,6 +1330,11 @@
       <c r="U10" t="n">
         <v>1</v>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396558O/3m-polyester-overlaminating-film-7732fl.pdf?&amp;fn=3M-Polyester-Overlaminating-Film-7732FL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1378,6 +1423,11 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399695O/3m-computer-imprintable-polyester-label-material-7880hl.pdf?&amp;fn=3M-Computer-Imprintable-Polyester-Label-Material-7880HL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1433,6 +1483,11 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1516,6 +1571,11 @@
       <c r="U13" t="n">
         <v>0</v>
       </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396566O/3m-durable-label-material-fm01972.pdf?&amp;fn=3M-Durable-Label-Material-FM01972.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1594,6 +1654,11 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396546O/3m-graffiti-resistant-overlaminating-durable-label-material-7248.pdf?&amp;fn=3M-Graffiti-Resistant-Overlaminating-Durable-Label-Material-7248.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1683,6 +1748,11 @@
       <c r="U15" t="n">
         <v>1</v>
       </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399680O/3m-thermal-transfer-polyester-label-material-7831.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7831.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1761,6 +1831,11 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396559O/3m-outdoor-ul-recognized-lexan-durable-label-material-ofl010n.pdf?&amp;fn=3M-Outdoor-UL-Recognized-Lexan-Durable-Label-Material-OFL010N.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1844,6 +1919,11 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399721O/3m-thermal-transfer-polyester-label-material-7864.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7864.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1928,6 +2008,11 @@
       <c r="U18" t="n">
         <v>0</v>
       </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2100,6 +2185,11 @@
       <c r="U20" t="n">
         <v>1</v>
       </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399671O/3m-screen-printable-sheet-vinyl-label-material-7904.pdf?&amp;fn=3M-Screen-Printable-Sheet-Vinyl-Label-Material-7904.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2183,6 +2273,11 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396514O/3m-screen-printable-polyester-performance-durable-label-material-7911fl.pdf?&amp;fn=3M-Screen-Printable-Polyester-Performance-Durable-Label-Material-7911FL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2271,6 +2366,11 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399699O/3m-screen-printable-sheet-vinyl-label-material-7901.pdf?&amp;fn=3M-Screen-Printable-Sheet-Vinyl-Label-Material-7901.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2355,6 +2455,11 @@
       <c r="U23" t="n">
         <v>0</v>
       </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396578O/3m-indoor-ul-recognized-computer-imprintable-white-polyester-durable-label-material-fm162.pdf?&amp;fn=3M-Indoor-UL-Recognized-Computer-Imprintable-White-Polyester-Durable-Label-Material-FM162.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2438,6 +2543,11 @@
       <c r="U24" t="n">
         <v>0</v>
       </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396582O/3m-screen-printable-polyester-performance-durable-label-material-with-structured-adhesive-7214sa.pdf?&amp;fn=3M-Screen-Printable-Polyester-Performance-Durable-Label-Material-with-Structured-Adhesive-7214SA.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2516,6 +2626,11 @@
       <c r="U25" t="n">
         <v>0</v>
       </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/230721O/soft-translucent-vinyl-label-product-fv172-fv173.pdf?&amp;fn=70071111606.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2599,6 +2714,11 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399684O/3m-thermal-transfer-polyester-label-material-7879fl.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7879FL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2688,6 +2808,11 @@
       <c r="U27" t="n">
         <v>1</v>
       </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2772,6 +2897,11 @@
       <c r="U28" t="n">
         <v>1</v>
       </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396528O/3m-velvet-textured-polycarbonate-overlaminating-film-7737fl.pdf?&amp;fn=3M-Velvet-Textured-Polycarbonate-Overlaminating-Film-7737FL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2934,6 +3064,11 @@
       <c r="U30" t="n">
         <v>0</v>
       </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396536O/3m-indoor-ul-recognized-clear-polyester-overlaminate-durable-label-material-fm011.pdf?&amp;fn=3M-Indoor-UL-Recognized-Clear-Polyester-Overlaminate-Durable-Label-Material-FM011.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3017,6 +3152,11 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399716O/3m-thermal-transfer-polyester-label-material-7871fl.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7871FL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3100,6 +3240,11 @@
       <c r="U32" t="n">
         <v>0</v>
       </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/121769O/laser-toner-polyester-label-material-7840-7840tl.pdf?&amp;fn=70070910396.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3184,6 +3329,11 @@
       <c r="U33" t="n">
         <v>0</v>
       </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396583O/3m-durable-label-material-fp035402.pdf?&amp;fn=3M-Durable-Label-Material-FP035402.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3278,6 +3428,11 @@
       <c r="U34" t="n">
         <v>1</v>
       </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399697O/3m-screen-printable-sheet-polyester-label-material-7907.pdf?&amp;fn=3M-Screen-Printable-Sheet-Polyester-Label-Material-7907.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3367,6 +3522,11 @@
       <c r="U35" t="n">
         <v>1</v>
       </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399681O/3m-durable-label-material-7840hl.pdf?&amp;fn=3M-Durable-Label-Material-7840HL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3445,6 +3605,11 @@
       <c r="U36" t="n">
         <v>0</v>
       </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3528,6 +3693,11 @@
       <c r="U37" t="n">
         <v>0</v>
       </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3611,6 +3781,11 @@
       <c r="U38" t="n">
         <v>0</v>
       </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3694,6 +3869,11 @@
       <c r="U39" t="n">
         <v>0</v>
       </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399665O/3m-durable-label-material-7850tl.pdf?&amp;fn=3M-Durable-Label-Material-7850TL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3774,6 +3954,11 @@
       <c r="U40" t="n">
         <v>0</v>
       </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1019592O/product-article-letter-ij39.pdf?&amp;fn=IJ39-Article-Letter.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3857,6 +4042,11 @@
       <c r="U41" t="n">
         <v>0</v>
       </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396576O/3m-screen-printable-vinyl-performance-durable-label-material-7053.pdf?&amp;fn=3M-Screen-Printable-Vinyl-Performance-Durable-Label-Material-7053.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3940,6 +4130,11 @@
       <c r="U42" t="n">
         <v>0</v>
       </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399711O/3m-polypropylene-label-material-76716na.pdf?&amp;fn=3M-Polypropylene-Label-Material-76716NA.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4013,6 +4208,11 @@
       <c r="U43" t="n">
         <v>0</v>
       </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396571O/3m-destructible-acetate-durable-label-material-fa112.pdf?&amp;fn=3M-Destructible-Acetate-Durable-Label-Material-FA112.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4096,6 +4296,11 @@
       <c r="U44" t="n">
         <v>0</v>
       </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396553O/3m-screen-printable-polyester-performance-durable-label-material-with-structured-adhesive-7218sa.pdf?&amp;fn=3M-Screen-Printable-Polyester-Performance-Durable-Label-Material-with-Structured-Adhesive-7218SA.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4184,6 +4389,11 @@
       <c r="U45" t="n">
         <v>0</v>
       </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399698O/3m-screen-printable-sheet-polyester-label-material-7950.pdf?&amp;fn=3M-Screen-Printable-Sheet-Polyester-Label-Material-7950.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4272,6 +4482,11 @@
       <c r="U46" t="n">
         <v>0</v>
       </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396509O/3m-screen-printable-polyester-performance-durable-label-material-7028.pdf?&amp;fn=3M-Screen-Printable-Polyester-Performance-Durable-Label-Material-7028.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4355,6 +4570,11 @@
       <c r="U47" t="n">
         <v>0</v>
       </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399701O/3m-thermal-transfer-polyester-label-material-7873.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7873.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4438,6 +4658,11 @@
       <c r="U48" t="n">
         <v>0</v>
       </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399726O/3m-performance-paper-label-material-7011.pdf?&amp;fn=3M-Performance-Paper-Label-Material-7011.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4521,6 +4746,11 @@
       <c r="U49" t="n">
         <v>0</v>
       </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396560O/3m-screen-printable-vinyl-performance-label-material-7051.pdf?&amp;fn=3M-Screen-Printable-Vinyl-Performance-Label-Material-7051.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4601,6 +4831,11 @@
       <c r="U50" t="n">
         <v>0</v>
       </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396563O/3m-screen-printable-polyester-performance-durable-label-material-with-structured-adhesive-7215sa.pdf?&amp;fn=3M-Screen-Printable-Polyester-Performance-Durable-Label-Material-with-Structured-Adhesive-7215SA.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4684,6 +4919,11 @@
       <c r="U51" t="n">
         <v>0</v>
       </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/121776O/3m-thermal-transfer-polyester-label-material-7331fl.pdf?&amp;fn=70070910230.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4767,6 +5007,11 @@
       <c r="U52" t="n">
         <v>0</v>
       </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396581O/3m-tamper-indicating-label-material-7384.pdf?&amp;fn=3M-Tamper-Indicating-Label-Material-7384.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4933,6 +5178,11 @@
       <c r="U54" t="n">
         <v>0</v>
       </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5003,6 +5253,11 @@
       <c r="U55" t="n">
         <v>0</v>
       </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5081,6 +5336,11 @@
       <c r="U56" t="n">
         <v>0</v>
       </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396533O/3m-velvet-textured-polycarbonate-overlaminating-film-7738fl.pdf?&amp;fn=3M-Velvet-Textured-Polycarbonate-Overlaminating-Film-7738FL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5156,6 +5416,11 @@
       <c r="U57" t="n">
         <v>0</v>
       </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399723O/3m-polyester-overlaminating-film-7744.pdf?&amp;fn=3M-Polyester-Overlaminating-Film-7744.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5234,6 +5499,11 @@
       <c r="U58" t="n">
         <v>0</v>
       </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1455463O/3m-wash-away-label-fp0602.pdf?&amp;fn=FP0602-Data-Sheet.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5314,6 +5584,11 @@
       <c r="U59" t="n">
         <v>0</v>
       </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396535O/3m-durable-label-material-7819.pdf?&amp;fn=3M-Durable-Label-Material-7819.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5397,6 +5672,11 @@
       <c r="U60" t="n">
         <v>0</v>
       </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399704O/3m-durable-label-material-7850hl.pdf?&amp;fn=3M-Durable-Label-Material-7850HL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5480,6 +5760,11 @@
       <c r="U61" t="n">
         <v>0</v>
       </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1455463O/3m-wash-away-label-fp0602.pdf?&amp;fn=FP0602-Data-Sheet.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5563,6 +5848,11 @@
       <c r="U62" t="n">
         <v>0</v>
       </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399715O/3m-thermal-transfer-polyester-label-material-7874.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7874.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5646,6 +5936,11 @@
       <c r="U63" t="n">
         <v>0</v>
       </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399688O/3m-thermal-transfer-polyester-label-material-7879.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7879.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5804,6 +6099,11 @@
       <c r="U65" t="n">
         <v>0</v>
       </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1455465O/3m-double-linered-adhesive-transfer-tape-ff002702-10.pdf?&amp;fn=FF002702-10-Data-Sheet.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5877,6 +6177,11 @@
       <c r="U66" t="n">
         <v>0</v>
       </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396593O/3m-lexan-durable-label-material-fl01n.pdf?&amp;fn=3M-Lexan-Durable-Label-Material-FL01N.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5960,6 +6265,11 @@
       <c r="U67" t="n">
         <v>0</v>
       </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396562O/3m-mc-polyester-durable-label-material-fm01961k.pdf?&amp;fn=3M-MC-Polyester-Durable-Label-Material-FM01961K.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6038,6 +6348,11 @@
       <c r="U68" t="n">
         <v>0</v>
       </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6122,6 +6437,11 @@
       <c r="U69" t="n">
         <v>0</v>
       </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396552O/3m-clear-polyester-durable-label-material-fm042.pdf?&amp;fn=3M-Clear-Polyester-Durable-Label-Material-FM042.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6205,6 +6525,11 @@
       <c r="U70" t="n">
         <v>0</v>
       </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6278,6 +6603,11 @@
       <c r="U71" t="n">
         <v>0</v>
       </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396594O/3m-indoor-ul-recognized-matte-clear-polyester-overlaminate-durable-label-material-fm071.pdf?&amp;fn=3M-Indoor-UL-Recognized-Matte-Clear-Polyester-Overlaminate-Durable-Label-Material-FM071.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6353,6 +6683,11 @@
       <c r="U72" t="n">
         <v>0</v>
       </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396516O/3m-clear-polyester-durable-label-material-fm1542.pdf?&amp;fn=3M-Clear-Polyester-Durable-Label-Material-FM1542.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6433,6 +6768,11 @@
       <c r="U73" t="n">
         <v>0</v>
       </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396580O/3m-indoor-ul-recognized-computer-imprintable-white-polyester-durable-label-material-fm16k.pdf?&amp;fn=3M-Indoor-UL-Recognized-Computer-Imprintable-White-Polyester-Durable-Label-Material-FM16K.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6516,6 +6856,11 @@
       <c r="U74" t="n">
         <v>0</v>
       </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396586O/3m-white-polyester-durable-label-material-fm1732r.pdf?&amp;fn=3M-White-Polyester-Durable-Label-Material-FM1732R.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6599,6 +6944,11 @@
       <c r="U75" t="n">
         <v>0</v>
       </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396530O/3m-indoor-ul-recognized-matte-clear-polyester-durable-label-material-fm232.pdf?&amp;fn=3M-Indoor-UL-Recognized-Matte-Clear-Polyester-Durable-Label-Material-FM232.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6682,6 +7032,11 @@
       <c r="U76" t="n">
         <v>0</v>
       </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6757,6 +7112,11 @@
       <c r="U77" t="n">
         <v>0</v>
       </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396569O/3m-matte-white-polypropylene-durable-label-material-fp010609.pdf?&amp;fn=3M-Matte-White-Polypropylene-Durable-Label-Material-FP010609.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6837,6 +7197,11 @@
       <c r="U78" t="n">
         <v>0</v>
       </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396579O/3m-removable-white-polypropylene-label-material-fp018209.pdf?&amp;fn=3M-Removable-White-Polypropylene-Label-Material-FP018209.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6912,6 +7277,11 @@
       <c r="U79" t="n">
         <v>0</v>
       </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1455463O/3m-wash-away-label-fp0602.pdf?&amp;fn=FP0602-Data-Sheet.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6992,6 +7362,11 @@
       <c r="U80" t="n">
         <v>0</v>
       </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7075,6 +7450,11 @@
       <c r="U81" t="n">
         <v>0</v>
       </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/287319O/white-polypropylene-label-product-fp027202.pdf?&amp;fn=70071113164.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7153,6 +7533,11 @@
       <c r="U82" t="n">
         <v>0</v>
       </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/492321O/white-metallized-polypropylene-label-pro-fp032302-032302w-032305.pdf?&amp;fn=70071345113.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7231,6 +7616,11 @@
       <c r="U83" t="n">
         <v>0</v>
       </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396517O/3m-clear-polypropylene-durable-label-material-fp102.pdf?&amp;fn=3M-Clear-Polypropylene-Durable-Label-Material-FP102.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7314,6 +7704,11 @@
       <c r="U84" t="n">
         <v>0</v>
       </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396549O/3m-removable-clear-polypropylene-durable-label-material-fp56n.pdf?&amp;fn=3M-Removable-Clear-Polypropylene-Durable-Label-Material-FP56N.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7394,6 +7789,11 @@
       <c r="U85" t="n">
         <v>0</v>
       </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7472,6 +7872,11 @@
       <c r="U86" t="n">
         <v>0</v>
       </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/226580O/white-vinyl-label-products-fv023202-205-702.pdf?&amp;fn=70071111135.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7552,6 +7957,11 @@
       <c r="U87" t="n">
         <v>0</v>
       </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7635,6 +8045,11 @@
       <c r="U88" t="n">
         <v>0</v>
       </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396513O/3m-removable-vinyl-durable-label-material-fv1222.pdf?&amp;fn=3M-Removable-Vinyl-Durable-Label-Material-FV1222.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7713,6 +8128,11 @@
       <c r="U89" t="n">
         <v>0</v>
       </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7796,6 +8216,11 @@
       <c r="U90" t="n">
         <v>0</v>
       </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396551O/3m-outdoor-ul-recognized-white-polyester-durable-label-material-ofm03402.pdf?&amp;fn=3M-Outdoor-UL-Recognized-White-Polyester-Durable-Label-Material-OFM03402.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7879,6 +8304,11 @@
       <c r="U91" t="n">
         <v>0</v>
       </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7962,6 +8392,11 @@
       <c r="U92" t="n">
         <v>0</v>
       </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396511O/3m-durable-label-material-ofm2402-silver-polyester.pdf?&amp;fn=3M-Durable-Label-Material-OFM2402-Silver-Polyester.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8027,6 +8462,11 @@
       <c r="U93" t="n">
         <v>0</v>
       </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1455465O/3m-double-linered-adhesive-transfer-tape-ff002702-10.pdf?&amp;fn=FF002702-10-Data-Sheet.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8107,6 +8547,11 @@
       <c r="U94" t="n">
         <v>0</v>
       </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8182,6 +8627,11 @@
       <c r="U95" t="n">
         <v>0</v>
       </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8260,6 +8710,11 @@
       <c r="U96" t="n">
         <v>0</v>
       </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1578062O/3m-durable-label-material-fs042.pdf?&amp;fn=3M-Durable-Label-Material-FS042.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8335,6 +8790,11 @@
       <c r="U97" t="n">
         <v>0</v>
       </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1455463O/3m-wash-away-label-fp0602.pdf?&amp;fn=FP0602-Data-Sheet.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8418,6 +8878,11 @@
       <c r="U98" t="n">
         <v>0</v>
       </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8493,6 +8958,11 @@
       <c r="U99" t="n">
         <v>0</v>
       </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1455465O/3m-double-linered-adhesive-transfer-tape-ff002702-10.pdf?&amp;fn=FF002702-10-Data-Sheet.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8578,6 +9048,11 @@
       <c r="U100" t="n">
         <v>0</v>
       </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396590O/3m-screen-printable-extended-life-vinyl-performance-durable-label-material-7049.pdf?&amp;fn=3M-Screen-Printable-Extended-Life-Vinyl-Performance-Durable-Label-Material-7049.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8667,6 +9142,11 @@
       <c r="U101" t="n">
         <v>1</v>
       </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1455463O/3m-wash-away-label-fp0602.pdf?&amp;fn=FP0602-Data-Sheet.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8740,6 +9220,11 @@
       <c r="U102" t="n">
         <v>0</v>
       </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396526O/3m-indoor-ul-recognized-lexan-durable-label-material-fl02n.pdf?&amp;fn=3M-Indoor-UL-Recognized-Lexan-Durable-Label-Material-FL02N.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8829,6 +9314,11 @@
       <c r="U103" t="n">
         <v>1</v>
       </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1561216O/3m-durable-label-materials.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7818.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8914,6 +9404,11 @@
       <c r="U104" t="n">
         <v>0</v>
       </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8997,6 +9492,11 @@
       <c r="U105" t="n">
         <v>0</v>
       </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399689O/3m-versatile-print-label-material-7903v.pdf?&amp;fn=3M-Versatile-Print-Label-Material-7903V.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9080,6 +9580,11 @@
       <c r="U106" t="n">
         <v>0</v>
       </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399727O/3m-versatile-print-label-material-7905v.pdf?&amp;fn=3M-Versatile-Print-Label-Material-7905V.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9210,6 +9715,11 @@
       <c r="U108" t="n">
         <v>0</v>
       </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9270,6 +9780,11 @@
       <c r="U109" t="n">
         <v>0</v>
       </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9335,6 +9850,11 @@
       <c r="U110" t="n">
         <v>0</v>
       </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9400,6 +9920,11 @@
       <c r="U111" t="n">
         <v>0</v>
       </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9465,6 +9990,11 @@
       <c r="U112" t="n">
         <v>0</v>
       </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9530,6 +10060,11 @@
       <c r="U113" t="n">
         <v>0</v>
       </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1302803O/3m-fire-protection-products-specifiers-guide.pdf?&amp;fn=3M-Fire-Protection-Products-Specifiers-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9610,6 +10145,11 @@
       <c r="U114" t="n">
         <v>0</v>
       </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396541O/3m-destructible-polyurethane-label-material-3812.pdf?&amp;fn=3M-Destructible-Polyurethane-Label-Material-3812.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9699,6 +10239,11 @@
       <c r="U115" t="n">
         <v>1</v>
       </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396585O/3m-tamper-indicating-label-material-7381-7866.pdf?&amp;fn=3M-Tamper-Indicating-Label-Material-7381-7866.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9788,6 +10333,11 @@
       <c r="U116" t="n">
         <v>1</v>
       </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396557O/3m-destructible-vinyl-label-material-7613t.pdf?&amp;fn=3M-Destructible-Vinyl-Label-Material-7613T.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9871,6 +10421,11 @@
       <c r="U117" t="n">
         <v>0</v>
       </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396545O/3m-destructible-vinyl-label-material-7930t.pdf?&amp;fn=3M-Destructible-Vinyl-Label-Material-7930T.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9960,6 +10515,11 @@
       <c r="U118" t="n">
         <v>1</v>
       </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396584O/3m-void-polyester-durable-label-material-7380.pdf?&amp;fn=3M-Void-Polyester-Durable-Label-Material-7380.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10049,6 +10609,11 @@
       <c r="U119" t="n">
         <v>1</v>
       </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396544O/3m-tamper-indicating-label-material-7935.pdf?&amp;fn=3M-Tamper-Indicating-Label-Material-7935.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10211,6 +10776,11 @@
       <c r="U121" t="n">
         <v>0</v>
       </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396534O/3m-pet-durable-label-material-8417.pdf?&amp;fn=3M-PET-Durable-Label-Material-8417.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10289,6 +10859,11 @@
       <c r="U122" t="n">
         <v>0</v>
       </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396561O/3m-polyester-overlaminating-film-7741.pdf?&amp;fn=3M-Polyester-Overlaminating-Film-7741.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10378,6 +10953,11 @@
       <c r="U123" t="n">
         <v>1</v>
       </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399709O/3m-polyester-overlaminating-film-7745fl.pdf?&amp;fn=3M-Polyester-Overlaminating-Film-7745FL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10462,6 +11042,11 @@
       <c r="U124" t="n">
         <v>1</v>
       </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396568O/3m-polyester-overlaminating-film-7730fl.pdf?&amp;fn=3M-Polyester-Overlaminating-Film-7730FL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10545,6 +11130,11 @@
       <c r="U125" t="n">
         <v>0</v>
       </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396555O/3m-uv-resistant-polyester-overlaminating-film-7733fl.pdf?&amp;fn=3M-UV-Resistant-Polyester-Overlaminating-Film-7733FL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10623,6 +11213,11 @@
       <c r="U126" t="n">
         <v>0</v>
       </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396543O/3m-polyester-overlaminating-film-7742.pdf?&amp;fn=3M-Polyester-Overlaminating-Film-7742.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10712,6 +11307,11 @@
       <c r="U127" t="n">
         <v>1</v>
       </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399710O/3m-polyester-overlaminating-film-7744fl.pdf?&amp;fn=3M-Polyester-Overlaminating-Film-7744FL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10791,6 +11391,11 @@
       <c r="U128" t="n">
         <v>0</v>
       </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396587O/3m-textured-vinyl-durable-label-material-fv02490n.pdf?&amp;fn=3M-Textured-Vinyl-Durable-Label-Material-FV02490N.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10880,6 +11485,11 @@
       <c r="U129" t="n">
         <v>1</v>
       </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399720O/3m-thermal-transfer-polyester-label-material-7875.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7875.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10969,6 +11579,11 @@
       <c r="U130" t="n">
         <v>1</v>
       </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399713O/3m-thermal-transfer-polyester-label-material-7816.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7816.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -11058,6 +11673,11 @@
       <c r="U131" t="n">
         <v>1</v>
       </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399705O/3m-thermal-transfer-polyester-label-material-7813.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7813.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -11147,6 +11767,11 @@
       <c r="U132" t="n">
         <v>1</v>
       </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399700O/3m-thermal-transfer-polyester-label-material-7810.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7810.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -11236,6 +11861,11 @@
       <c r="U133" t="n">
         <v>1</v>
       </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396572O/3m-outdoor-ul-recognized-brushed-silver-polyester-durable-label-material-ofm2902.pdf?&amp;fn=3M-Outdoor-UL-Recognized-Brushed-Silver-Polyester-Durable-Label-Material-OFM2902.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11330,6 +11960,11 @@
       <c r="U134" t="n">
         <v>1</v>
       </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396542O/3m-outdoor-ul-recognized-clear-polyester-durable-label-material-ofm3102.pdf?&amp;fn=3M-Outdoor-UL-Recognized-Clear-Polyester-Durable-Label-Material-OFM3102.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11419,6 +12054,11 @@
       <c r="U135" t="n">
         <v>1</v>
       </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399673O/3m-polypropylene-label-material-7776.pdf?&amp;fn=3M-Polypropylene-Label-Material-7776.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11508,6 +12148,11 @@
       <c r="U136" t="n">
         <v>1</v>
       </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399696O/3m-thermal-transfer-polyester-label-material-7872.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7872.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11597,6 +12242,11 @@
       <c r="U137" t="n">
         <v>1</v>
       </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399677O/3m-thermal-transfer-polyester-label-material-7871.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7871.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11681,6 +12331,11 @@
       <c r="U138" t="n">
         <v>0</v>
       </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1455463O/3m-wash-away-label-fp0602.pdf?&amp;fn=FP0602-Data-Sheet.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11770,6 +12425,11 @@
       <c r="U139" t="n">
         <v>1</v>
       </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396574O/3m-polypropylene-label-material-7777.pdf?&amp;fn=3M-Polypropylene-Label-Material-7777.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11859,6 +12519,11 @@
       <c r="U140" t="n">
         <v>1</v>
       </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399686O/3m-thermal-transfer-acrylate-label-material-3921.pdf?&amp;fn=3M-Thermal-Transfer-Acrylate-Label-Material-3921.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11942,6 +12607,11 @@
       <c r="U141" t="n">
         <v>0</v>
       </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396532O/3m-durable-label-material-ofm2802-silver-polyester.pdf?&amp;fn=3M-Durable-Label-Material-OFM2802-Silver-Polyester.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12025,6 +12695,11 @@
       <c r="U142" t="n">
         <v>0</v>
       </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396529O/3m-durable-label-material-ofv0202.pdf?&amp;fn=3M-Durable-Label-Material-OFV0202.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -12114,6 +12789,11 @@
       <c r="U143" t="n">
         <v>1</v>
       </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399687O/3m-thermal-transfer-polyester-label-material-7876.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7876.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -12203,6 +12883,11 @@
       <c r="U144" t="n">
         <v>1</v>
       </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1455463O/3m-wash-away-label-fp0602.pdf?&amp;fn=FP0602-Data-Sheet.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -12292,6 +12977,11 @@
       <c r="U145" t="n">
         <v>1</v>
       </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1455463O/3m-wash-away-label-fp0602.pdf?&amp;fn=FP0602-Data-Sheet.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -12381,6 +13071,11 @@
       <c r="U146" t="n">
         <v>1</v>
       </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399712O/3m-performance-paper-label-material-7000.pdf?&amp;fn=3M-Performance-Paper-Label-Material-7000.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12470,6 +13165,11 @@
       <c r="U147" t="n">
         <v>1</v>
       </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396554O/3m-screen-printable-polyester-performance-durable-label-material-7029.pdf?&amp;fn=3M-Screen-Printable-Polyester-Performance-Durable-Label-Material-7029.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12553,6 +13253,11 @@
       <c r="U148" t="n">
         <v>0</v>
       </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396570O/3m-screen-printable-polyester-performance-durable-label-material-7034.pdf?&amp;fn=3M-Screen-Printable-Polyester-Performance-Durable-Label-Material-7034.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -12641,6 +13346,11 @@
       <c r="U149" t="n">
         <v>0</v>
       </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396521O/3m-screen-printable-polyester-performance-durable-label-material-7033.pdf?&amp;fn=3M-Screen-Printable-Polyester-Performance-Durable-Label-Material-7033.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -12729,6 +13439,11 @@
       <c r="U150" t="n">
         <v>0</v>
       </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396577O/3m-screen-printable-polyester-performance-durable-label-material-7037.pdf?&amp;fn=3M-Screen-Printable-Polyester-Performance-Durable-Label-Material-7037.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -12818,6 +13533,11 @@
       <c r="U151" t="n">
         <v>1</v>
       </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396527O/3m-screen-printable-vinyl-performance-durable-label-material-7045.pdf?&amp;fn=3M-Screen-Printable-Vinyl-Performance-Durable-Label-Material-7045.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12907,6 +13627,11 @@
       <c r="U152" t="n">
         <v>1</v>
       </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399675O/3m-performance-paper-label-material-7110.pdf?&amp;fn=3M-Performance-Paper-Label-Material-7110.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -12995,6 +13720,11 @@
       <c r="U153" t="n">
         <v>0</v>
       </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396588O/3m-screen-printable-polyester-performance-durable-label-material-with-structured-adhesive-7220sa.pdf?&amp;fn=3M-Screen-Printable-Polyester-Performance-Durable-Label-Material-with-Structured-Adhesive-7220SA.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -13084,6 +13814,11 @@
       <c r="U154" t="n">
         <v>1</v>
       </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399676O/3m-removable-vinyl-label-material-7600.pdf?&amp;fn=3M-Removable-Vinyl-Label-Material-7600.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -13173,6 +13908,11 @@
       <c r="U155" t="n">
         <v>1</v>
       </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396538O/3m-laser-markable-label-material-7847.pdf?&amp;fn=3M-Laser-Markable-Label-Material-7847.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -13267,6 +14007,11 @@
       <c r="U156" t="n">
         <v>1</v>
       </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399718O/3m-sheet-label-material-7903.pdf?&amp;fn=3M-Sheet-Label-Material-7903.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -13355,6 +14100,11 @@
       <c r="U157" t="n">
         <v>0</v>
       </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399691O/3m-sheet-label-material-7905.pdf?&amp;fn=3M-Sheet-Label-Material-7905.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -13449,6 +14199,11 @@
       <c r="U158" t="n">
         <v>1</v>
       </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399719O/3m-sheet-label-material-7908.pdf?&amp;fn=3M-Sheet-Label-Material-7908.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -13537,6 +14292,11 @@
       <c r="U159" t="n">
         <v>0</v>
       </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399722O/3m-sheet-label-material-7909.pdf?&amp;fn=3M-Sheet-Label-Material-7909.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -13625,6 +14385,11 @@
       <c r="U160" t="n">
         <v>0</v>
       </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399670O/3m-sheet-label-material-7903fl.pdf?&amp;fn=3M-Sheet-Label-Material-7903FL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -13713,6 +14478,11 @@
       <c r="U161" t="n">
         <v>0</v>
       </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399730O/3m-sheet-label-material-7908fl.pdf?&amp;fn=3M-Sheet-Label-Material-7908FL.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -13801,6 +14571,11 @@
       <c r="U162" t="n">
         <v>0</v>
       </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396537O/3m-aluminum-foil-label-material-7940.pdf?&amp;fn=3M-Aluminum-Foil-Label-Material-7940.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -13895,6 +14670,11 @@
       <c r="U163" t="n">
         <v>1</v>
       </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399678O/3m-computer-imprintable-polyester-label-material-7880.pdf?&amp;fn=3M-Computer-Imprintable-Polyester-Label-Material-7880.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -13983,6 +14763,11 @@
       <c r="U164" t="n">
         <v>0</v>
       </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399679O/3m-computer-imprintable-polyester-label-material-7881.pdf?&amp;fn=3M-Computer-Imprintable-Polyester-Label-Material-7881.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -14077,6 +14862,11 @@
       <c r="U165" t="n">
         <v>1</v>
       </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399692O/3m-computer-imprintable-polyester-label-material-7883.pdf?&amp;fn=3M-Computer-Imprintable-Polyester-Label-Material-7883.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -14165,6 +14955,11 @@
       <c r="U166" t="n">
         <v>0</v>
       </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399693O/3m-screen-printable-sheet-polyester-label-material-7924.pdf?&amp;fn=3M-Screen-Printable-Sheet-Polyester-Label-Material-7924.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -14347,6 +15142,11 @@
       <c r="U168" t="n">
         <v>1</v>
       </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399669O/3m-screen-printable-sheet-polyester-label-material-7980.pdf?&amp;fn=3M-Screen-Printable-Sheet-Polyester-Label-Material-7980.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -14441,6 +15241,11 @@
       <c r="U169" t="n">
         <v>1</v>
       </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399674O/3m-screen-printable-sheet-polyester-label-material-7983.pdf?&amp;fn=3M-Screen-Printable-Sheet-Polyester-Label-Material-7983.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -14530,6 +15335,11 @@
       <c r="U170" t="n">
         <v>1</v>
       </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396589O/3m-removable-white-polypropylene-durable-label-material-fp016902.pdf?&amp;fn=3M-Removable-White-Polypropylene-Durable-Label-Material-FP016902.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -14619,6 +15429,11 @@
       <c r="U171" t="n">
         <v>1</v>
       </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396520O/3m-removable-clear-polypropylene-durable-label-material-fp0862.pdf?&amp;fn=3M-Removable-Clear-Polypropylene-Durable-Label-Material-FP0862.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -14697,6 +15512,11 @@
       <c r="U172" t="n">
         <v>0</v>
       </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396518O/3m-vinyl-durable-label-material-fv027805.pdf?&amp;fn=3M-Vinyl-Durable-Label-Material-FV027805.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -14785,6 +15605,11 @@
       <c r="U173" t="n">
         <v>0</v>
       </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399690O/3m-versatile-print-label-material-7871v.pdf?&amp;fn=3M-Versatile-Print-Label-Material-7871V.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -14868,6 +15693,11 @@
       <c r="U174" t="n">
         <v>0</v>
       </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399717O/3m-versatile-print-label-material-7908v.pdf?&amp;fn=3M-Versatile-Print-Label-Material-7908V.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -14951,6 +15781,11 @@
       <c r="U175" t="n">
         <v>0</v>
       </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399707O/3m-versatile-print-label-material-7872v.pdf?&amp;fn=3M-Versatile-Print-Label-Material-7872V.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -15031,6 +15866,11 @@
       <c r="U176" t="n">
         <v>0</v>
       </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399724O/3m-versatile-print-label-material-7816v.pdf?&amp;fn=3M-Versatile-Print-Label-Material-7816V.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -15119,6 +15959,11 @@
       <c r="U177" t="n">
         <v>0</v>
       </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396510O/3m-versatile-print-label-material-7868v.pdf?&amp;fn=3M-Versatile-Print-Label-Material-7868V.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -15202,6 +16047,11 @@
       <c r="U178" t="n">
         <v>0</v>
       </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399708O/3m-versatile-print-label-material-7875v.pdf?&amp;fn=3M-Versatile-Print-Label-Material-7875V.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -15285,6 +16135,11 @@
       <c r="U179" t="n">
         <v>0</v>
       </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2396591O/3m-screen-printable-vinyl-performance-label-material-7051sa.pdf?&amp;fn=3M-Screen-Printable-Vinyl-Performance-Label-Material-7051SA.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -15368,6 +16223,11 @@
       <c r="U180" t="n">
         <v>0</v>
       </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399666O/3m-versatile-print-label-material-7876v.pdf?&amp;fn=3M-Versatile-Print-Label-Material-7876V.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -15433,6 +16293,11 @@
       <c r="U181" t="n">
         <v>0</v>
       </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399702O/3m-versatile-print-label-material-7909v.pdf?&amp;fn=3M-Versatile-Print-Label-Material-7909V.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -15517,6 +16382,11 @@
       <c r="U182" t="n">
         <v>0</v>
       </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -15678,6 +16548,11 @@
       <c r="U184" t="n">
         <v>0</v>
       </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/1017875O/3m-converter-markets-selection-guide-july-2023.pdf?&amp;fn=3M-Converter-Markets-Guide.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -15767,6 +16642,11 @@
       <c r="U185" t="n">
         <v>1</v>
       </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2399703O/3m-thermal-transfer-polyester-label-material-7868.pdf?&amp;fn=3M-Thermal-Transfer-Polyester-Label-Material-7868.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -15850,6 +16730,11 @@
       <c r="U186" t="n">
         <v>0</v>
       </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/66593O/thermal-transfer-polyester-label-material-7350-7861.pdf?&amp;fn=70070910248.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -16100,6 +16985,11 @@
       </c>
       <c r="U189" t="n">
         <v>0</v>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>https://multimedia.3m.com/mws/media/2606075O/3m-versatile-print-label-material-7331v.pdf?&amp;fn=3M-Versatile-Print-Label-Material-7331V.pdf</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/import/3m.xlsx
+++ b/data/import/3m.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V189"/>
+  <dimension ref="A1:W189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,11 @@
           <t>tds</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/data/import/3m.xlsx
+++ b/data/import/3m.xlsx
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I7" t="n">
         <v>125</v>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I8" t="n">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I10" t="n">
         <v>125</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I15" t="n">
         <v>125</v>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I18" t="n">
         <v>60</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I20" t="n">
         <v>60</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I27" t="n">
         <v>60</v>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I30" t="n">
         <v>125</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I69" t="n">
         <v>125</v>
@@ -10287,7 +10287,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I116" t="n">
         <v>60</v>
@@ -10472,7 +10472,7 @@
         <v>-40</v>
       </c>
       <c r="I118" t="n">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>-40</v>
       </c>
       <c r="I120" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I123" t="n">
         <v>125</v>
@@ -11001,7 +11001,7 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I124" t="n">
         <v>125</v>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I127" t="n">
         <v>125</v>
@@ -11350,7 +11350,7 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I128" t="n">
         <v>60</v>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I134" t="n">
         <v>125</v>
@@ -12008,10 +12008,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I135" t="n">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>-40</v>
       </c>
       <c r="I136" t="n">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>-40</v>
       </c>
       <c r="I138" t="n">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -12379,10 +12379,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I139" t="n">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I143" t="n">
         <v>125</v>
@@ -13028,7 +13028,7 @@
         <v>-40</v>
       </c>
       <c r="I146" t="n">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I147" t="n">
         <v>125</v>
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I151" t="n">
         <v>60</v>
@@ -13584,7 +13584,7 @@
         <v>-40</v>
       </c>
       <c r="I152" t="n">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>-40</v>
       </c>
       <c r="I154" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I170" t="n">
         <v>60</v>
@@ -15383,7 +15383,7 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I171" t="n">
         <v>60</v>
@@ -16336,7 +16336,7 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>89</v>
+        <v>-29</v>
       </c>
       <c r="I182" t="n">
         <v>60</v>
